--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40241-2026 artfynd.xlsx
+++ b/artfynd/A 40241-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857950</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857951</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136858031</v>
       </c>
       <c r="B4" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>136858032</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
